--- a/registers/test_tasker.xlsx
+++ b/registers/test_tasker.xlsx
@@ -46,13 +46,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -330,25 +329,25 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="26" customWidth="1" style="4" min="1" max="2"/>
-    <col width="25.63" customWidth="1" style="4" min="3" max="3"/>
+    <col width="26" customWidth="1" style="3" min="1" max="2"/>
+    <col width="25.63" customWidth="1" style="3" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ESTATUS</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>FECHA DE ACTUALIZACION</t>
         </is>
@@ -360,13 +359,13 @@
           <t>TICKET-41720</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>Under Construction</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>45581.83177073507</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>45633.62745731875</v>
       </c>
     </row>
     <row r="3">
@@ -375,13 +374,13 @@
           <t>TICKET-41722</t>
         </is>
       </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>45581.83181266692</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>45633.62745766807</v>
       </c>
     </row>
     <row r="4">
@@ -390,13 +389,13 @@
           <t>TICKET-67884</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>Under Construction</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>45581.83185421918</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>45633.62745806559</v>
       </c>
     </row>
     <row r="5">
@@ -405,110 +404,1439 @@
           <t>TICKET-49485</t>
         </is>
       </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>45581.83189614901</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>45633.62745839146</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TICKET-52034</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>45581.83193844016</v>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>45633.62745876185</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TICKET-57093</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>Under Construction</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>45581.83197990471</v>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>45633.62745906566</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TICKET-59023</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>Under Construction</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>45581.83202125879</v>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>45633.62745945333</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TICKET-13454</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>Ready to Integrate</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>45581.83206242023</v>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>45633.62745976511</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TICKET-39567</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>45581.83210380485</v>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>45633.62746006605</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TICKET-50768</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>Under Construction</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>45581.83214532902</v>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>45633.62746044159</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>45633.62746077371</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>45633.62746114506</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>45633.62746155739</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>45633.62746185424</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>45633.62746224798</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>45633.62746256047</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>45633.62746291929</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>45633.62746322022</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>45633.62746354428</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>45633.62746385677</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>45633.62746418086</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>45633.62746449356</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>45633.62746488688</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>45633.62746522253</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>45633.62746555837</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>45633.62746592854</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>45633.62746626419</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>45633.62746663475</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>45633.62746695868</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>45633.62746730605</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>45633.6274677112</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>45633.62746811605</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>45633.62746844037</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>45633.62746878734</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>45633.62746911174</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>45633.62746948181</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>45633.62746984059</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>45633.62747023429</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>45633.62747055817</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>45633.62747094037</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>45633.62747133362</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>45633.62747168085</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>45633.62747207472</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>45633.62747243317</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>45633.62747275725</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>45633.62747313919</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>45633.6274734519</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>45633.62747381048</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>45633.62747416928</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>45633.6274745515</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>45633.62747485218</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>45633.62747521096</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>45633.62747556975</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>45633.62747592854</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>45633.62747628259</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>45633.62747661113</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>45633.62747693469</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>45633.62747726312</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>45633.62747764826</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>45633.6274779628</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>45633.62747831685</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>45633.62747869389</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>45633.62747907203</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>45633.62747944979</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>45633.62747983655</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>45633.62748021058</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>45633.62748051174</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>45633.62748081615</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>45633.62748116337</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>45633.62748154531</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>45633.62748192529</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>45633.62748226315</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>45633.62748257494</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>45633.62748290424</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>45633.62748320536</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>45633.62748358639</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>45633.62748397631</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>45633.6274843206</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>45633.62748465734</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>45633.62748499435</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>45633.62748530456</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>45633.6274856452</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>45633.62748603826</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>45633.62748640709</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>45633.62748671739</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>45633.62748707819</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>45633.62748744105</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>45633.62748774198</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>45633.62748805468</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>45633.62748839934</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>45633.62748872007</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>45633.62748905089</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41720</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>45633.6274893634</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-41722</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Under Construction</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>45633.62748972217</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-67884</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ready to Integrate</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>45633.62749010217</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="n">
+        <v>45633.62749041386</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>45633.62749070466</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>45633.62749100963</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>TICKET-49485</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>45633.62749131973</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -522,6 +1850,95 @@
     <hyperlink ref="A9" r:id="rId8"/>
     <hyperlink ref="A10" r:id="rId9"/>
     <hyperlink ref="A11" r:id="rId10"/>
+    <hyperlink ref="A12" r:id="rId11"/>
+    <hyperlink ref="A13" r:id="rId12"/>
+    <hyperlink ref="A14" r:id="rId13"/>
+    <hyperlink ref="A15" r:id="rId14"/>
+    <hyperlink ref="A16" r:id="rId15"/>
+    <hyperlink ref="A17" r:id="rId16"/>
+    <hyperlink ref="A18" r:id="rId17"/>
+    <hyperlink ref="A19" r:id="rId18"/>
+    <hyperlink ref="A20" r:id="rId19"/>
+    <hyperlink ref="A21" r:id="rId20"/>
+    <hyperlink ref="A22" r:id="rId21"/>
+    <hyperlink ref="A23" r:id="rId22"/>
+    <hyperlink ref="A24" r:id="rId23"/>
+    <hyperlink ref="A25" r:id="rId24"/>
+    <hyperlink ref="A26" r:id="rId25"/>
+    <hyperlink ref="A27" r:id="rId26"/>
+    <hyperlink ref="A28" r:id="rId27"/>
+    <hyperlink ref="A29" r:id="rId28"/>
+    <hyperlink ref="A30" r:id="rId29"/>
+    <hyperlink ref="A31" r:id="rId30"/>
+    <hyperlink ref="A32" r:id="rId31"/>
+    <hyperlink ref="A33" r:id="rId32"/>
+    <hyperlink ref="A34" r:id="rId33"/>
+    <hyperlink ref="A35" r:id="rId34"/>
+    <hyperlink ref="A36" r:id="rId35"/>
+    <hyperlink ref="A37" r:id="rId36"/>
+    <hyperlink ref="A38" r:id="rId37"/>
+    <hyperlink ref="A39" r:id="rId38"/>
+    <hyperlink ref="A40" r:id="rId39"/>
+    <hyperlink ref="A41" r:id="rId40"/>
+    <hyperlink ref="A42" r:id="rId41"/>
+    <hyperlink ref="A43" r:id="rId42"/>
+    <hyperlink ref="A44" r:id="rId43"/>
+    <hyperlink ref="A45" r:id="rId44"/>
+    <hyperlink ref="A46" r:id="rId45"/>
+    <hyperlink ref="A47" r:id="rId46"/>
+    <hyperlink ref="A48" r:id="rId47"/>
+    <hyperlink ref="A49" r:id="rId48"/>
+    <hyperlink ref="A50" r:id="rId49"/>
+    <hyperlink ref="A51" r:id="rId50"/>
+    <hyperlink ref="A52" r:id="rId51"/>
+    <hyperlink ref="A53" r:id="rId52"/>
+    <hyperlink ref="A54" r:id="rId53"/>
+    <hyperlink ref="A55" r:id="rId54"/>
+    <hyperlink ref="A56" r:id="rId55"/>
+    <hyperlink ref="A57" r:id="rId56"/>
+    <hyperlink ref="A58" r:id="rId57"/>
+    <hyperlink ref="A59" r:id="rId58"/>
+    <hyperlink ref="A60" r:id="rId59"/>
+    <hyperlink ref="A61" r:id="rId60"/>
+    <hyperlink ref="A62" r:id="rId61"/>
+    <hyperlink ref="A63" r:id="rId62"/>
+    <hyperlink ref="A64" r:id="rId63"/>
+    <hyperlink ref="A65" r:id="rId64"/>
+    <hyperlink ref="A66" r:id="rId65"/>
+    <hyperlink ref="A67" r:id="rId66"/>
+    <hyperlink ref="A68" r:id="rId67"/>
+    <hyperlink ref="A69" r:id="rId68"/>
+    <hyperlink ref="A70" r:id="rId69"/>
+    <hyperlink ref="A71" r:id="rId70"/>
+    <hyperlink ref="A72" r:id="rId71"/>
+    <hyperlink ref="A73" r:id="rId72"/>
+    <hyperlink ref="A74" r:id="rId73"/>
+    <hyperlink ref="A75" r:id="rId74"/>
+    <hyperlink ref="A76" r:id="rId75"/>
+    <hyperlink ref="A77" r:id="rId76"/>
+    <hyperlink ref="A78" r:id="rId77"/>
+    <hyperlink ref="A79" r:id="rId78"/>
+    <hyperlink ref="A80" r:id="rId79"/>
+    <hyperlink ref="A81" r:id="rId80"/>
+    <hyperlink ref="A82" r:id="rId81"/>
+    <hyperlink ref="A83" r:id="rId82"/>
+    <hyperlink ref="A84" r:id="rId83"/>
+    <hyperlink ref="A85" r:id="rId84"/>
+    <hyperlink ref="A86" r:id="rId85"/>
+    <hyperlink ref="A87" r:id="rId86"/>
+    <hyperlink ref="A88" r:id="rId87"/>
+    <hyperlink ref="A89" r:id="rId88"/>
+    <hyperlink ref="A90" r:id="rId89"/>
+    <hyperlink ref="A91" r:id="rId90"/>
+    <hyperlink ref="A92" r:id="rId91"/>
+    <hyperlink ref="A93" r:id="rId92"/>
+    <hyperlink ref="A94" r:id="rId93"/>
+    <hyperlink ref="A95" r:id="rId94"/>
+    <hyperlink ref="A96" r:id="rId95"/>
+    <hyperlink ref="A97" r:id="rId96"/>
+    <hyperlink ref="A98" r:id="rId97"/>
+    <hyperlink ref="A99" r:id="rId98"/>
+    <hyperlink ref="A100" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
